--- a/research/traditional_assets/database/data/kenya/kenya_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_insurance_life.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0572</v>
+        <v>0.117</v>
       </c>
       <c r="G2">
-        <v>0.07622857142857142</v>
+        <v>0.0145985401459854</v>
       </c>
       <c r="H2">
-        <v>0.07622857142857142</v>
+        <v>0.0145985401459854</v>
       </c>
       <c r="I2">
-        <v>0.068</v>
+        <v>0.0077007299270073</v>
       </c>
       <c r="J2">
-        <v>0.034</v>
+        <v>0.0077007299270073</v>
       </c>
       <c r="K2">
-        <v>-1.07</v>
+        <v>-3.54</v>
       </c>
       <c r="L2">
-        <v>-0.01222857142857143</v>
+        <v>-0.0322992700729927</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,52 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.6</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="W2">
-        <v>-0.07535211267605635</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.2370356631577427</v>
-      </c>
-      <c r="Y2">
-        <v>-0.3123877758337991</v>
-      </c>
-      <c r="Z2">
-        <v>2.868852459016394</v>
-      </c>
-      <c r="AA2">
-        <v>0.09754098360655739</v>
+        <v>0.16246278397103</v>
       </c>
       <c r="AB2">
-        <v>0.1166026443509015</v>
-      </c>
-      <c r="AC2">
-        <v>-0.01906166074434407</v>
+        <v>0.16246278397103</v>
       </c>
       <c r="AD2">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>8.899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.6597222222222222</v>
-      </c>
-      <c r="AI2">
-        <v>0.6521739130434783</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.3771186440677966</v>
-      </c>
-      <c r="AK2">
-        <v>0.3692946058091286</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.81</v>
+        <v>3.82</v>
       </c>
       <c r="AM2">
-        <v>2.81</v>
+        <v>3.82</v>
       </c>
       <c r="AN2">
-        <v>4.272863568215892</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>2.117437722419929</v>
+        <v>0.2209424083769634</v>
       </c>
       <c r="AP2">
-        <v>1.334332833583208</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>2.117437722419929</v>
+        <v>0.2209424083769634</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +695,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0572</v>
+        <v>0.117</v>
       </c>
       <c r="G3">
-        <v>0.07622857142857142</v>
+        <v>0.0145985401459854</v>
       </c>
       <c r="H3">
-        <v>0.07622857142857142</v>
+        <v>0.0145985401459854</v>
       </c>
       <c r="I3">
-        <v>0.068</v>
+        <v>0.0077007299270073</v>
       </c>
       <c r="J3">
-        <v>0.034</v>
+        <v>0.0077007299270073</v>
       </c>
       <c r="K3">
-        <v>-1.07</v>
+        <v>-3.54</v>
       </c>
       <c r="L3">
-        <v>-0.01222857142857143</v>
+        <v>-0.0322992700729927</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +737,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.6</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="W3">
-        <v>-0.07535211267605635</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.2370356631577427</v>
-      </c>
-      <c r="Y3">
-        <v>-0.3123877758337991</v>
-      </c>
-      <c r="Z3">
-        <v>2.868852459016394</v>
-      </c>
-      <c r="AA3">
-        <v>0.09754098360655739</v>
+        <v>0.16246278397103</v>
       </c>
       <c r="AB3">
-        <v>0.1166026443509015</v>
-      </c>
-      <c r="AC3">
-        <v>-0.01906166074434407</v>
+        <v>0.16246278397103</v>
       </c>
       <c r="AD3">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>8.899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.6597222222222222</v>
-      </c>
-      <c r="AI3">
-        <v>0.6521739130434783</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.3771186440677966</v>
-      </c>
-      <c r="AK3">
-        <v>0.3692946058091286</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>2.81</v>
+        <v>3.82</v>
       </c>
       <c r="AM3">
-        <v>2.81</v>
+        <v>3.82</v>
       </c>
       <c r="AN3">
-        <v>4.272863568215892</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>2.117437722419929</v>
+        <v>0.2209424083769634</v>
       </c>
       <c r="AP3">
-        <v>1.334332833583208</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>2.117437722419929</v>
+        <v>0.2209424083769634</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_insurance_life.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.117</v>
+        <v>0.0886</v>
       </c>
       <c r="G2">
-        <v>0.0145985401459854</v>
+        <v>0.07869955156950673</v>
       </c>
       <c r="H2">
-        <v>0.0145985401459854</v>
+        <v>0.07869955156950673</v>
       </c>
       <c r="I2">
-        <v>0.0077007299270073</v>
+        <v>0.07152466367713003</v>
       </c>
       <c r="J2">
-        <v>0.0077007299270073</v>
+        <v>0.03576233183856502</v>
       </c>
       <c r="K2">
-        <v>-3.54</v>
+        <v>-0.092</v>
       </c>
       <c r="L2">
-        <v>-0.0322992700729927</v>
+        <v>-0.001031390134529148</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -636,10 +636,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.16246278397103</v>
+        <v>0.1486037346692675</v>
       </c>
       <c r="AB2">
-        <v>0.16246278397103</v>
+        <v>0.1486037346692675</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,22 +660,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AM2">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>0.2209424083769634</v>
+        <v>1.687830687830688</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.2209424083769634</v>
+        <v>1.687830687830688</v>
       </c>
     </row>
     <row r="3">
@@ -695,25 +695,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.117</v>
+        <v>0.0886</v>
       </c>
       <c r="G3">
-        <v>0.0145985401459854</v>
+        <v>0.07869955156950673</v>
       </c>
       <c r="H3">
-        <v>0.0145985401459854</v>
+        <v>0.07869955156950673</v>
       </c>
       <c r="I3">
-        <v>0.0077007299270073</v>
+        <v>0.07152466367713003</v>
       </c>
       <c r="J3">
-        <v>0.0077007299270073</v>
+        <v>0.03576233183856502</v>
       </c>
       <c r="K3">
-        <v>-3.54</v>
+        <v>-0.092</v>
       </c>
       <c r="L3">
-        <v>-0.0322992700729927</v>
+        <v>-0.001031390134529148</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.16246278397103</v>
+        <v>0.1486037346692675</v>
       </c>
       <c r="AB3">
-        <v>0.16246278397103</v>
+        <v>0.1486037346692675</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -767,22 +767,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AM3">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>0.2209424083769634</v>
+        <v>1.687830687830688</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.2209424083769634</v>
+        <v>1.687830687830688</v>
       </c>
     </row>
   </sheetData>
